--- a/02_DIA_inicio_2026_analisis_assets/rbd_9704_escuela-lo-valledor_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9704_escuela-lo-valledor_nt1_rubricas.xlsx
@@ -1920,13 +1920,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A401987-6323-4AB2-9C97-045BB3EDAA51}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3237B9AF-858C-4D7C-A848-ED3E1E8EC2F8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758DFC63-81D7-460C-A7A9-900B4EEC0D63}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04E26A3D-A215-4BEB-89DA-F3DDB9175958}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D8FAD06-4A18-4E5C-9DF4-E4C7BB020887}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C7AF7A1-2F3B-424E-B2B6-643F648BC7E7}"/>
 </file>